--- a/docs/backend/쿠첸_API설계_v0.2.xlsx
+++ b/docs/backend/쿠첸_API설계_v0.2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jinhyeokheo/Roylabs/Project/cuchen2/docs/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1453813A-4657-3C4B-911D-76DFD10122F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8CE7C1-A52C-174F-AA53-B5E80B9744E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30240" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="257">
   <si>
     <t>이미지파일</t>
   </si>
@@ -467,15 +467,9 @@
     <t>MinIO 서버의 전체 접근 가능 버킷을 직접 조회하는 API는 아니다.</t>
   </si>
   <si>
-    <t>입력 폴더를 재귀 스캔해 MongoDB와 MinIO에 동기화하는 API</t>
-  </si>
-  <si>
     <t>POST /ingest/scan</t>
   </si>
   <si>
-    <t>요약: 입력 폴더 재귀 스캔 및 MongoDB/MinIO 동기화</t>
-  </si>
-  <si>
     <t>rootDir</t>
   </si>
   <si>
@@ -726,6 +720,96 @@
   </si>
   <si>
     <t>응답 형태는 /images/:imageId/metadata와 동일하다.</t>
+  </si>
+  <si>
+    <t>API 호출로 전달받은 path + filebase 파일 묶음을 MongoDB와 MinIO에 동기화한다. 기존 scan API는 보조 경로다.</t>
+  </si>
+  <si>
+    <t>요약: 입력 폴더 재귀 스캔 및 MongoDB/MinIO 동기화(보조 API)</t>
+  </si>
+  <si>
+    <t>/ingest/files</t>
+  </si>
+  <si>
+    <t>ingestFiles</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>요약: path + filebase 기준 4개 div 파일 묶음 동기화</t>
+  </si>
+  <si>
+    <t>Request Body</t>
+  </si>
+  <si>
+    <t>FIELD</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>Version A에서는 backend host/WSL 프로세스가 접근 가능한 실제 OS 경로. Version B에서는 컨테이너 내부 경로</t>
+  </si>
+  <si>
+    <t>filebase</t>
+  </si>
+  <si>
+    <t>div suffix 앞의 파일 base name. 예: cuchen-test</t>
+  </si>
+  <si>
+    <t>Required Files</t>
+  </si>
+  <si>
+    <t>{path}/{filebase}-top.png + {path}/{filebase}-top.json</t>
+  </si>
+  <si>
+    <t>{path}/{filebase}-bot.png + {path}/{filebase}-bot.json</t>
+  </si>
+  <si>
+    <t>{path}/{filebase}-top-inf.png + {path}/{filebase}-top-inf.json</t>
+  </si>
+  <si>
+    <t>{path}/{filebase}-bot-inf.png + {path}/{filebase}-bot-inf.json</t>
+  </si>
+  <si>
+    <t>Response Body</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>4개 div pair 중 일부 파일이 없으면 400 Bad Request로 거절하고 ingest를 시작하지 않는다.</t>
+  </si>
+  <si>
+    <t>성공한 입력 파일은 원본 위치에서 삭제한다.</t>
+  </si>
+  <si>
+    <t>실패한 pair는 입력 폴더 아래 failed/로 이동한다.</t>
+  </si>
+  <si>
+    <t>Version B Docker 실행형에서는 path가 컨테이너 내부 경로다. host 경로를 쓰려면 bind mount가 필요하다.</t>
+  </si>
+  <si>
+    <t>Runtime Versions</t>
+  </si>
+  <si>
+    <t>Version A</t>
+  </si>
+  <si>
+    <t>host/WSL 직접 실행. 현재 기본값. /mnt/c/... 같은 실제 OS 경로 사용 가능</t>
+  </si>
+  <si>
+    <t>Version B</t>
+  </si>
+  <si>
+    <t>Docker 실행 가능형. path는 컨테이너 내부 경로이며 host 경로는 bind mount 필요</t>
+  </si>
+  <si>
+    <t>path + filebase 기준 4개 div 파일 묶음 동기화</t>
+  </si>
+  <si>
+    <t>POST /ingest/files</t>
   </si>
 </sst>
 </file>
@@ -831,7 +915,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -935,12 +1019,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1035,26 +1128,49 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1062,26 +1178,29 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1091,26 +1210,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1279,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
@@ -1575,6 +1703,30 @@
       </c>
       <c r="G17" s="28" t="str">
         <f>HYPERLINK("#'이미지파일'!A43","열기")</f>
+        <v>열기</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30" customHeight="1">
+      <c r="A18" s="15">
+        <v>10</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="G18" s="28" t="str">
+        <f>HYPERLINK("#'인제스트'!A28","열기")</f>
         <v>열기</v>
       </c>
     </row>
@@ -1630,16 +1782,16 @@
       <c r="I2" s="20"/>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="16" t="s">
@@ -1651,13 +1803,13 @@
       <c r="C5" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
       <c r="A6" s="22" t="s">
@@ -1669,13 +1821,13 @@
       <c r="C6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1">
       <c r="A7" s="22" t="s">
@@ -1687,13 +1839,13 @@
       <c r="C7" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="37"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1">
       <c r="A8" s="22" t="s">
@@ -1705,13 +1857,13 @@
       <c r="C8" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
       <c r="A9" s="22" t="s">
@@ -1723,13 +1875,13 @@
       <c r="C9" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="37"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="22" t="s">
@@ -1741,25 +1893,25 @@
       <c r="C10" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="35" t="s">
+      <c r="D10" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="16" t="s">
@@ -1771,13 +1923,13 @@
       <c r="C14" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="22" t="s">
@@ -1789,13 +1941,13 @@
       <c r="C15" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="22" t="s">
@@ -1807,13 +1959,13 @@
       <c r="C16" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="22" t="s">
@@ -1825,13 +1977,13 @@
       <c r="C17" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="37"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="22" t="s">
@@ -1843,13 +1995,13 @@
       <c r="C18" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
       <c r="A19" s="22" t="s">
@@ -1861,13 +2013,13 @@
       <c r="C19" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
       <c r="A20" s="22" t="s">
@@ -1879,13 +2031,13 @@
       <c r="C20" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="D20" s="39" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
       <c r="A21" s="22" t="s">
@@ -1897,13 +2049,13 @@
       <c r="C21" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="35" t="s">
+      <c r="D21" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="30" t="s">
@@ -1915,13 +2067,13 @@
       <c r="C22" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="42" t="s">
+      <c r="D22" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="37"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="32" t="s">
@@ -1933,22 +2085,17 @@
       <c r="C23" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D17:H17"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="D8:H8"/>
@@ -1962,6 +2109,11 @@
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D17:H17"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2053,28 +2205,28 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="16" t="s">
@@ -2086,13 +2238,13 @@
       <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="15" t="s">
@@ -2104,25 +2256,25 @@
       <c r="C11" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D11" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="37"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="16" t="s">
@@ -2134,13 +2286,13 @@
       <c r="C14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="15" t="s">
@@ -2152,13 +2304,13 @@
       <c r="C15" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="15" t="s">
@@ -2170,13 +2322,13 @@
       <c r="C16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="15" t="s">
@@ -2188,13 +2340,13 @@
       <c r="C17" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="37"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="15" t="s">
@@ -2206,13 +2358,13 @@
       <c r="C18" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="15" t="s">
@@ -2224,53 +2376,53 @@
       <c r="C19" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="37"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1">
       <c r="A23" s="15">
         <v>1</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="26" spans="1:8" ht="18" customHeight="1">
       <c r="A26" s="13" t="s">
@@ -2311,28 +2463,28 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1">
-      <c r="A29" s="39" t="s">
+      <c r="A29" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
-      <c r="A31" s="33" t="s">
+      <c r="A31" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
       <c r="A32" s="16" t="s">
@@ -2344,13 +2496,13 @@
       <c r="C32" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="37"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="41"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="15" t="s">
@@ -2362,25 +2514,25 @@
       <c r="C33" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="45" t="s">
+      <c r="D33" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="37"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="16" t="s">
@@ -2392,13 +2544,13 @@
       <c r="C36" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D36" s="44" t="s">
+      <c r="D36" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="37"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="15" t="s">
@@ -2410,13 +2562,13 @@
       <c r="C37" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="45" t="s">
+      <c r="D37" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="37"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="14" t="s">
@@ -2424,56 +2576,68 @@
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
       <c r="A40" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="37"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1">
       <c r="A41" s="15">
         <v>1</v>
       </c>
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="37"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="41"/>
     </row>
     <row r="42" spans="1:8" ht="31" customHeight="1">
       <c r="A42" s="31">
         <v>2</v>
       </c>
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="37"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="B23:H23"/>
@@ -2484,20 +2648,8 @@
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="B41:H41"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="D16:H16"/>
     <mergeCell ref="D37:H37"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="A9:H9"/>
     <mergeCell ref="B40:H40"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D19:H19"/>
     <mergeCell ref="D36:H36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -2506,8 +2658,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
@@ -2539,7 +2691,7 @@
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -2552,7 +2704,7 @@
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
@@ -2589,28 +2741,28 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
-      <c r="A7" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+      <c r="A7" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="16" t="s">
@@ -2622,17 +2774,17 @@
       <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="22" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>17</v>
@@ -2640,35 +2792,35 @@
       <c r="C11" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="37"/>
+      <c r="D11" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="37"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="16" t="s">
@@ -2680,17 +2832,17 @@
       <c r="C14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>101</v>
@@ -2698,17 +2850,17 @@
       <c r="C15" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
+      <c r="D15" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>101</v>
@@ -2716,17 +2868,17 @@
       <c r="C16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
+      <c r="D16" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="22" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>101</v>
@@ -2734,17 +2886,17 @@
       <c r="C17" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="37"/>
+      <c r="D17" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>101</v>
@@ -2752,17 +2904,17 @@
       <c r="C18" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="D18" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="22" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>101</v>
@@ -2770,94 +2922,523 @@
       <c r="C19" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="D19" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="37"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1">
       <c r="A23" s="22">
         <v>1</v>
       </c>
-      <c r="B23" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
+      <c r="B23" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1">
       <c r="A24" s="22">
         <v>2</v>
       </c>
-      <c r="B24" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="37"/>
+      <c r="B24" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1">
       <c r="A25" s="22">
         <v>3</v>
       </c>
-      <c r="B25" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="37"/>
+      <c r="B25" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
+    </row>
+    <row r="28" spans="1:8" ht="18" customHeight="1">
+      <c r="A28" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+    </row>
+    <row r="29" spans="1:8" ht="16" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="30" customHeight="1">
+      <c r="A30" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1">
+      <c r="A32" s="45" t="s">
+        <v>233</v>
+      </c>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1">
+      <c r="A33" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
+    </row>
+    <row r="34" spans="1:8" ht="30" customHeight="1">
+      <c r="A34" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
+    </row>
+    <row r="35" spans="1:8" ht="30" customHeight="1">
+      <c r="A35" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="41"/>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1">
+      <c r="A37" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="B37" s="43"/>
+      <c r="C37" s="43"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+    </row>
+    <row r="38" spans="1:8" ht="30" customHeight="1">
+      <c r="A38" s="22">
+        <v>1</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="41"/>
+    </row>
+    <row r="39" spans="1:8" ht="30" customHeight="1">
+      <c r="A39" s="22">
+        <v>2</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
+    </row>
+    <row r="40" spans="1:8" ht="30" customHeight="1">
+      <c r="A40" s="22">
+        <v>3</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
+    </row>
+    <row r="41" spans="1:8" ht="30" customHeight="1">
+      <c r="A41" s="22">
+        <v>4</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="41"/>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1">
+      <c r="A43" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="B43" s="43"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="43"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="43"/>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1">
+      <c r="A44" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="41"/>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1">
+      <c r="A45" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="41"/>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1">
+      <c r="A46" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="41"/>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1">
+      <c r="A47" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="41"/>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1">
+      <c r="A48" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="41"/>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1">
+      <c r="A49" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
+    </row>
+    <row r="52" spans="1:8" ht="15" customHeight="1">
+      <c r="A52" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
+    </row>
+    <row r="53" spans="1:8" ht="30" customHeight="1">
+      <c r="A53" s="22">
+        <v>1</v>
+      </c>
+      <c r="B53" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="C53" s="40"/>
+      <c r="D53" s="40"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
+    </row>
+    <row r="54" spans="1:8" ht="30" customHeight="1">
+      <c r="A54" s="22">
+        <v>2</v>
+      </c>
+      <c r="B54" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="41"/>
+    </row>
+    <row r="55" spans="1:8" ht="30" customHeight="1">
+      <c r="A55" s="22">
+        <v>3</v>
+      </c>
+      <c r="B55" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="41"/>
+    </row>
+    <row r="56" spans="1:8" ht="45" customHeight="1">
+      <c r="A56" s="22">
+        <v>4</v>
+      </c>
+      <c r="B56" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="41"/>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1">
+      <c r="A58" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+    </row>
+    <row r="59" spans="1:8" ht="30" customHeight="1">
+      <c r="A59" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="B59" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="41"/>
+    </row>
+    <row r="60" spans="1:8" ht="30" customHeight="1">
+      <c r="A60" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="B60" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="43">
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="D33:H33"/>
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D17:H17"/>
@@ -2874,8 +3455,16 @@
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B56:H56"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B60:H60"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2916,7 +3505,7 @@
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -2929,7 +3518,7 @@
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
@@ -2966,28 +3555,28 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
-      <c r="A7" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+      <c r="A7" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="16" t="s">
@@ -2999,13 +3588,13 @@
       <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="22" t="s">
@@ -3017,13 +3606,13 @@
       <c r="C11" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="37"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="22" t="s">
@@ -3035,17 +3624,17 @@
       <c r="C12" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="37"/>
+      <c r="D12" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
       <c r="A13" s="22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>17</v>
@@ -3053,13 +3642,13 @@
       <c r="C13" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="37"/>
+      <c r="D13" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="41"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="22" t="s">
@@ -3071,17 +3660,17 @@
       <c r="C14" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+      <c r="D14" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="22" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>17</v>
@@ -3089,17 +3678,17 @@
       <c r="C15" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
+      <c r="D15" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>17</v>
@@ -3107,17 +3696,17 @@
       <c r="C16" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
+      <c r="D16" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="31" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>17</v>
@@ -3125,17 +3714,17 @@
       <c r="C17" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
+      <c r="D17" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>17</v>
@@ -3143,17 +3732,17 @@
       <c r="C18" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="D18" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
       <c r="A19" s="22" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>17</v>
@@ -3161,17 +3750,17 @@
       <c r="C19" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="D19" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
       <c r="A20" s="22" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>17</v>
@@ -3179,17 +3768,17 @@
       <c r="C20" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="D20" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
       <c r="A21" s="22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>101</v>
@@ -3197,17 +3786,17 @@
       <c r="C21" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
+      <c r="D21" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
       <c r="A22" s="22" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B22" s="22" t="s">
         <v>101</v>
@@ -3215,13 +3804,13 @@
       <c r="C22" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="37"/>
+      <c r="D22" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
       <c r="A23" s="22" t="s">
@@ -3233,13 +3822,13 @@
       <c r="C23" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
+      <c r="D23" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
       <c r="A24" s="22" t="s">
@@ -3251,13 +3840,13 @@
       <c r="C24" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="50"/>
+      <c r="D24" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="59"/>
       <c r="I24" s="24"/>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
@@ -3270,26 +3859,26 @@
       <c r="C25" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="50"/>
+      <c r="D25" s="39" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="59"/>
       <c r="I25" s="24"/>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="60" t="s">
+      <c r="A26" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="60"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
       <c r="A27" s="16" t="s">
@@ -3301,17 +3890,17 @@
       <c r="C27" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="37"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
     </row>
     <row r="28" spans="1:9" ht="15" customHeight="1">
       <c r="A28" s="22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>101</v>
@@ -3319,17 +3908,17 @@
       <c r="C28" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="37"/>
+      <c r="D28" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
       <c r="A29" s="22" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>101</v>
@@ -3337,13 +3926,13 @@
       <c r="C29" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="37"/>
+      <c r="D29" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="41"/>
       <c r="I29" s="24"/>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1">
@@ -3356,148 +3945,155 @@
       <c r="C30" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="37"/>
+      <c r="D30" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="41"/>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1">
-      <c r="A31" s="61"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="59"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="56"/>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1">
       <c r="A32" s="22"/>
-      <c r="B32" s="36"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="37"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="41"/>
     </row>
     <row r="33" spans="1:9" ht="31" customHeight="1">
       <c r="A33" s="22"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="37"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" spans="1:9" ht="15">
-      <c r="A34" s="60" t="s">
+      <c r="A34" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="60"/>
-      <c r="G34" s="60"/>
-      <c r="H34" s="60"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
     </row>
     <row r="35" spans="1:9" ht="15">
       <c r="A35" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="38" t="s">
+      <c r="B35" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="37"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="41"/>
     </row>
     <row r="36" spans="1:9" ht="31" customHeight="1">
       <c r="A36" s="22">
         <v>1</v>
       </c>
-      <c r="B36" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="37"/>
+      <c r="B36" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
     </row>
     <row r="37" spans="1:9" ht="45" customHeight="1">
       <c r="A37" s="22">
         <v>2</v>
       </c>
-      <c r="B37" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="59"/>
+      <c r="B37" s="54" t="s">
+        <v>190</v>
+      </c>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="56"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1">
       <c r="A38" s="22">
         <v>3</v>
       </c>
-      <c r="B38" s="57" t="s">
-        <v>193</v>
-      </c>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="59"/>
+      <c r="B38" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="56"/>
     </row>
     <row r="39" spans="1:9" ht="31" customHeight="1">
       <c r="A39" s="31">
         <v>4</v>
       </c>
-      <c r="B39" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="C39" s="54"/>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="55"/>
+      <c r="B39" s="63" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="65"/>
     </row>
     <row r="40" spans="1:9" ht="31" customHeight="1">
-      <c r="A40" s="52">
+      <c r="A40" s="36">
         <v>5</v>
       </c>
-      <c r="B40" s="56" t="s">
-        <v>195</v>
-      </c>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
+      <c r="B40" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="61"/>
+      <c r="G40" s="61"/>
+      <c r="H40" s="61"/>
       <c r="I40" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A34:H34"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="B35:H35"/>
     <mergeCell ref="D11:H11"/>
@@ -3514,18 +4110,11 @@
     <mergeCell ref="D24:H24"/>
     <mergeCell ref="D29:H29"/>
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="B37:H37"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3566,7 +4155,7 @@
     </row>
     <row r="2" spans="1:9" ht="16.5" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B2" s="20"/>
       <c r="C2" s="20"/>
@@ -3579,7 +4168,7 @@
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1">
       <c r="A4" s="21" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="21"/>
@@ -3616,28 +4205,28 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
-      <c r="A7" s="39" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+      <c r="A7" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="16" t="s">
@@ -3649,13 +4238,13 @@
       <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="22" t="s">
@@ -3667,35 +4256,35 @@
       <c r="C11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="37"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="37"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="16" t="s">
@@ -3707,13 +4296,13 @@
       <c r="C14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="22" t="s">
@@ -3725,13 +4314,13 @@
       <c r="C15" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
+      <c r="D15" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="22" t="s">
@@ -3743,17 +4332,17 @@
       <c r="C16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
+      <c r="D16" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="22" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>17</v>
@@ -3761,17 +4350,17 @@
       <c r="C17" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="37"/>
+      <c r="D17" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
       <c r="A18" s="22" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B18" s="22" t="s">
         <v>17</v>
@@ -3779,17 +4368,17 @@
       <c r="C18" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="D18" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>17</v>
@@ -3797,17 +4386,17 @@
       <c r="C19" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="D19" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" ht="15" customHeight="1">
       <c r="A20" s="22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" s="22" t="s">
         <v>17</v>
@@ -3815,17 +4404,17 @@
       <c r="C20" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="D20" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1">
       <c r="A21" s="22" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B21" s="22" t="s">
         <v>17</v>
@@ -3833,53 +4422,53 @@
       <c r="C21" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
+      <c r="D21" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1">
       <c r="A22" s="22" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C22" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="37"/>
+      <c r="D22" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1">
       <c r="A23" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
+      <c r="D23" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1">
       <c r="A24" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B24" s="22" t="s">
         <v>93</v>
@@ -3887,17 +4476,17 @@
       <c r="C24" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="37"/>
+      <c r="D24" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1">
       <c r="A25" s="22" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B25" s="22" t="s">
         <v>17</v>
@@ -3905,35 +4494,35 @@
       <c r="C25" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="37"/>
+      <c r="D25" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1">
       <c r="A26" s="22" t="s">
         <v>97</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C26" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="37"/>
+      <c r="D26" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="41"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1">
       <c r="A27" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B27" s="22" t="s">
         <v>17</v>
@@ -3941,17 +4530,17 @@
       <c r="C27" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="37"/>
+      <c r="D27" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
       <c r="A28" s="22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B28" s="22" t="s">
         <v>17</v>
@@ -3959,87 +4548,87 @@
       <c r="C28" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="37"/>
+      <c r="D28" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="22"/>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="37"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="41"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
-      <c r="A30" s="33" t="s">
+      <c r="A30" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="37"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" ht="30" customHeight="1">
       <c r="A32" s="22">
         <v>1</v>
       </c>
-      <c r="B32" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="37"/>
+      <c r="B32" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="41"/>
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1">
       <c r="A33" s="23"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="37"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" spans="1:8" ht="30" customHeight="1">
       <c r="A34" s="23"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="37"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8" ht="18" customHeight="1">
       <c r="A35" s="21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B35" s="21"/>
       <c r="C35" s="21"/>
@@ -4086,16 +4675,16 @@
       <c r="H37" s="24"/>
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1">
-      <c r="A38" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
+      <c r="A38" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="24"/>
@@ -4108,16 +4697,16 @@
       <c r="H39" s="24"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
-      <c r="A40" s="33" t="s">
+      <c r="A40" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
       <c r="A41" s="16" t="s">
@@ -4129,13 +4718,13 @@
       <c r="C41" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D41" s="38" t="s">
+      <c r="D41" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="37"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="41"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
       <c r="A42" s="22" t="s">
@@ -4147,35 +4736,35 @@
       <c r="C42" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="37"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
       <c r="A43" s="22"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="37"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="41"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
-      <c r="A44" s="33" t="s">
+      <c r="A44" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
+      <c r="B44" s="43"/>
+      <c r="C44" s="43"/>
+      <c r="D44" s="43"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="43"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
       <c r="A45" s="16" t="s">
@@ -4187,13 +4776,13 @@
       <c r="C45" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D45" s="38" t="s">
+      <c r="D45" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="37"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="41"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
       <c r="A46" s="22" t="s">
@@ -4205,13 +4794,13 @@
       <c r="C46" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="37"/>
+      <c r="D46" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="41"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
       <c r="A47" s="22" t="s">
@@ -4223,17 +4812,17 @@
       <c r="C47" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="37"/>
+      <c r="D47" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="41"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
       <c r="A48" s="22" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B48" s="22" t="s">
         <v>17</v>
@@ -4241,17 +4830,17 @@
       <c r="C48" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="35" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="37"/>
+      <c r="D48" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="41"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="22" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B49" s="22" t="s">
         <v>17</v>
@@ -4259,17 +4848,17 @@
       <c r="C49" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D49" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="37"/>
+      <c r="D49" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B50" s="22" t="s">
         <v>17</v>
@@ -4277,17 +4866,17 @@
       <c r="C50" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="37"/>
+      <c r="D50" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="22" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B51" s="22" t="s">
         <v>17</v>
@@ -4295,17 +4884,17 @@
       <c r="C51" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="37"/>
+      <c r="D51" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
       <c r="A52" s="22" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B52" s="22" t="s">
         <v>17</v>
@@ -4313,53 +4902,53 @@
       <c r="C52" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D52" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="37"/>
+      <c r="D52" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="41"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="22" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C53" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="37"/>
+      <c r="D53" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C54" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="37"/>
+      <c r="D54" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="41"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B55" s="22" t="s">
         <v>93</v>
@@ -4367,17 +4956,17 @@
       <c r="C55" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="37"/>
+      <c r="D55" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="41"/>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="22" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B56" s="22" t="s">
         <v>17</v>
@@ -4385,35 +4974,35 @@
       <c r="C56" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="37"/>
+      <c r="D56" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="41"/>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="22" t="s">
         <v>97</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C57" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="D57" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36"/>
-      <c r="H57" s="37"/>
+      <c r="D57" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="41"/>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
       <c r="A58" s="22" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B58" s="22" t="s">
         <v>17</v>
@@ -4421,17 +5010,17 @@
       <c r="C58" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="E58" s="36"/>
-      <c r="F58" s="36"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="37"/>
+      <c r="D58" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="41"/>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="22" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B59" s="22" t="s">
         <v>17</v>
@@ -4439,56 +5028,91 @@
       <c r="C59" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="37"/>
+      <c r="D59" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="41"/>
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
-      <c r="A60" s="33" t="s">
+      <c r="A60" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
+      <c r="B60" s="43"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="43"/>
+      <c r="H60" s="43"/>
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="38" t="s">
+      <c r="B61" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="37"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="41"/>
     </row>
     <row r="62" spans="1:8" ht="30" customHeight="1">
       <c r="A62" s="22">
         <v>1</v>
       </c>
-      <c r="B62" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="C62" s="36"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="36"/>
-      <c r="G62" s="36"/>
-      <c r="H62" s="37"/>
+      <c r="B62" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="D14:H14"/>
     <mergeCell ref="B62:H62"/>
     <mergeCell ref="D41:H41"/>
     <mergeCell ref="D48:H48"/>
@@ -4505,41 +5129,6 @@
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D55:H55"/>
     <mergeCell ref="D24:H24"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D21:H21"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4630,28 +5219,28 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="43"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="16" t="s">
@@ -4663,13 +5252,13 @@
       <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1">
       <c r="A11" s="22" t="s">
@@ -4681,35 +5270,35 @@
       <c r="C11" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="35" t="s">
+      <c r="D11" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="37"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1">
       <c r="A12" s="22"/>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="37"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1">
       <c r="A14" s="16" t="s">
@@ -4721,13 +5310,13 @@
       <c r="C14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1">
       <c r="A15" s="22" t="s">
@@ -4739,13 +5328,13 @@
       <c r="C15" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1">
       <c r="A16" s="22" t="s">
@@ -4757,83 +5346,83 @@
       <c r="C16" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="35" t="s">
+      <c r="D16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="37"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1">
       <c r="A19" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1">
       <c r="A20" s="22">
         <v>1</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1">
       <c r="A21" s="23"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1">
       <c r="A22" s="23"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="37"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" ht="18" customHeight="1">
       <c r="A23" s="21" t="s">
@@ -4884,16 +5473,16 @@
       <c r="H25" s="24"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="24"/>
@@ -4906,16 +5495,16 @@
       <c r="H27" s="24"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1">
-      <c r="A28" s="33" t="s">
+      <c r="A28" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="43"/>
+      <c r="H28" s="43"/>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1">
       <c r="A29" s="16" t="s">
@@ -4927,13 +5516,13 @@
       <c r="C29" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D29" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="37"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="41"/>
     </row>
     <row r="30" spans="1:8" ht="15" customHeight="1">
       <c r="A30" s="22" t="s">
@@ -4945,35 +5534,35 @@
       <c r="C30" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D30" s="35" t="s">
+      <c r="D30" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="37"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="41"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1">
       <c r="A31" s="22"/>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="37"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1">
-      <c r="A32" s="33" t="s">
+      <c r="A32" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
       <c r="A33" s="16" t="s">
@@ -4985,13 +5574,13 @@
       <c r="C33" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="37"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
       <c r="A34" s="22" t="s">
@@ -5003,13 +5592,13 @@
       <c r="C34" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="35" t="s">
+      <c r="D34" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="37"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
       <c r="A35" s="22" t="s">
@@ -5021,13 +5610,13 @@
       <c r="C35" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="35" t="s">
+      <c r="D35" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="37"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="41"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
       <c r="A36" s="22" t="s">
@@ -5039,83 +5628,83 @@
       <c r="C36" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="35" t="s">
+      <c r="D36" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="37"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
       <c r="A37" s="22"/>
       <c r="B37" s="22"/>
       <c r="C37" s="22"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="37"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
-      <c r="A38" s="33" t="s">
+      <c r="A38" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="43"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="43"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
       <c r="A39" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B39" s="38" t="s">
+      <c r="B39" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="37"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1">
       <c r="A40" s="22">
         <v>1</v>
       </c>
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="37"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1">
       <c r="A41" s="23"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="37"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="41"/>
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1">
       <c r="A42" s="23"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="37"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="40"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" ht="18" customHeight="1">
       <c r="A43" s="21" t="s">
@@ -5166,16 +5755,16 @@
       <c r="H45" s="24"/>
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1">
-      <c r="A46" s="39" t="s">
+      <c r="A46" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="24"/>
@@ -5188,16 +5777,16 @@
       <c r="H47" s="24"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
-      <c r="A48" s="33" t="s">
+      <c r="A48" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="43"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1">
       <c r="A49" s="16" t="s">
@@ -5209,13 +5798,13 @@
       <c r="C49" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D49" s="38" t="s">
+      <c r="D49" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="37"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
     </row>
     <row r="50" spans="1:8" ht="15" customHeight="1">
       <c r="A50" s="22" t="s">
@@ -5227,35 +5816,35 @@
       <c r="C50" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D50" s="35" t="s">
+      <c r="D50" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="37"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
     </row>
     <row r="51" spans="1:8" ht="15" customHeight="1">
       <c r="A51" s="22"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="37"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
     </row>
     <row r="52" spans="1:8" ht="15" customHeight="1">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="34"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="34"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="43"/>
     </row>
     <row r="53" spans="1:8" ht="15" customHeight="1">
       <c r="A53" s="16" t="s">
@@ -5267,13 +5856,13 @@
       <c r="C53" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D53" s="38" t="s">
+      <c r="D53" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="37"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1">
       <c r="A54" s="22" t="s">
@@ -5285,13 +5874,13 @@
       <c r="C54" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="35" t="s">
+      <c r="D54" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="37"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="41"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1">
       <c r="A55" s="22" t="s">
@@ -5303,13 +5892,13 @@
       <c r="C55" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="35" t="s">
+      <c r="D55" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="37"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="41"/>
     </row>
     <row r="56" spans="1:8" ht="15" customHeight="1">
       <c r="A56" s="22" t="s">
@@ -5321,66 +5910,95 @@
       <c r="C56" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="35" t="s">
+      <c r="D56" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="37"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="41"/>
     </row>
     <row r="57" spans="1:8" ht="15" customHeight="1">
       <c r="A57" s="22"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
-      <c r="D57" s="35"/>
-      <c r="E57" s="36"/>
-      <c r="F57" s="36"/>
-      <c r="G57" s="36"/>
-      <c r="H57" s="37"/>
+      <c r="D57" s="39"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="41"/>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1">
-      <c r="A58" s="33" t="s">
+      <c r="A58" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B59" s="38" t="s">
+      <c r="B59" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
-      <c r="H59" s="37"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="41"/>
     </row>
     <row r="60" spans="1:8" ht="30" customHeight="1">
       <c r="A60" s="22">
         <v>1</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="37"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="D56:H56"/>
     <mergeCell ref="B60:H60"/>
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D30:H30"/>
@@ -5397,35 +6015,6 @@
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="D50:H50"/>
     <mergeCell ref="A58:H58"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="B41:H41"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
